--- a/BWI/bestwine_output/bestwine_Venezuela.xlsx
+++ b/BWI/bestwine_output/bestwine_Venezuela.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA37"/>
+  <dimension ref="A1:AA38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -4298,6 +4298,91 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Importadora Vinum</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Importadora Vinum</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>108910</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Caracas</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Miranda, Chacao</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>C/C Calle Ernesto Blohm</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>1090</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>https://importadora-vinum.com</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>ventas@importadora-vinum.com</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>+58 212-9595065</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/importadora-vinum-c-a/</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinumccs</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCepG4B9lFZwDn_0qSK38qWg</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr"/>
+      <c r="X38" s="2" t="inlineStr"/>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
